--- a/activity/M01A04/M01A04_MDT.xlsx
+++ b/activity/M01A04/M01A04_MDT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4067A7FE-D437-4CFA-A76B-77DF5B988BD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36DECA66-AF6E-4100-AAE7-ABECE0E10A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificacion" sheetId="12" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="30">
   <si>
     <t>Observaciones</t>
   </si>
@@ -109,9 +109,6 @@
     <t>Calificación: 1.4. Modelo de terreno GIS 3D en estado natural (TIN) usando QGIS</t>
   </si>
   <si>
-    <t>https://github.com/rcfdtools/R.HCMC/blob/main/activity/M01A04/Readme.md</t>
-  </si>
-  <si>
     <t>Modificar la red de drenaje natural CGG_DrenajeNatural_v0.shp incluyendo el eje suavizado del valle a partir del eje de proyecto asignado y eliminando los tramos remanentes naturales que serán removidos por la explotación minera, nombrar como /file/shp/CGG_DrenajeNaturalValleSuavizado_v0.shp.</t>
   </si>
   <si>
@@ -141,7 +138,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -218,6 +215,12 @@
       <name val="Segoe UI Light"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF0070C0"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -233,7 +236,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -403,15 +406,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -563,25 +557,34 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -589,17 +592,8 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2011,7 +2005,7 @@
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.45">
       <c r="F1" s="29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.45">
@@ -2286,20 +2280,21 @@
       </c>
     </row>
     <row r="19" spans="2:6" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
+      <c r="B19" s="41" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
+        <v>Ir a actividad M01A04 en GitHub.</v>
+      </c>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="26"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B21" s="26"/>
@@ -2309,17 +2304,15 @@
       <c r="F21" s="26"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B2:F3"/>
     <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:F20"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="B19" r:id="rId1" xr:uid="{3ECDF22D-EF6A-4F28-9FDB-219744857DB6}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
-  <drawing r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2371,82 +2364,82 @@
     </row>
     <row r="2" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="36" t="str">
+      <c r="C2" s="39" t="str">
         <f>Calificacion!$B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="37"/>
-      <c r="E2" s="36" t="str">
+      <c r="D2" s="40"/>
+      <c r="E2" s="39" t="str">
         <f>Calificacion!$B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="F2" s="37"/>
-      <c r="G2" s="36" t="str">
+      <c r="F2" s="40"/>
+      <c r="G2" s="39" t="str">
         <f>Calificacion!$B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="H2" s="37"/>
-      <c r="I2" s="36" t="str">
+      <c r="H2" s="40"/>
+      <c r="I2" s="39" t="str">
         <f>Calificacion!$B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="J2" s="37"/>
-      <c r="K2" s="36" t="str">
+      <c r="J2" s="40"/>
+      <c r="K2" s="39" t="str">
         <f>Calificacion!$B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="L2" s="37"/>
-      <c r="M2" s="36" t="str">
+      <c r="L2" s="40"/>
+      <c r="M2" s="39" t="str">
         <f>Calificacion!$B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="N2" s="37"/>
-      <c r="O2" s="36" t="str">
+      <c r="N2" s="40"/>
+      <c r="O2" s="39" t="str">
         <f>Calificacion!$B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="36" t="str">
+      <c r="P2" s="40"/>
+      <c r="Q2" s="39" t="str">
         <f>Calificacion!$B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="R2" s="37"/>
-      <c r="S2" s="36" t="str">
+      <c r="R2" s="40"/>
+      <c r="S2" s="39" t="str">
         <f>Calificacion!$B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="T2" s="37"/>
-      <c r="U2" s="36" t="str">
+      <c r="T2" s="40"/>
+      <c r="U2" s="39" t="str">
         <f>Calificacion!$B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="V2" s="37"/>
-      <c r="W2" s="36" t="str">
+      <c r="V2" s="40"/>
+      <c r="W2" s="39" t="str">
         <f>Calificacion!$B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="X2" s="37"/>
-      <c r="Y2" s="36" t="str">
+      <c r="X2" s="40"/>
+      <c r="Y2" s="39" t="str">
         <f>Calificacion!$B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="Z2" s="37"/>
-      <c r="AA2" s="36" t="str">
+      <c r="Z2" s="40"/>
+      <c r="AA2" s="39" t="str">
         <f>Calificacion!$B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AB2" s="37"/>
-      <c r="AC2" s="36" t="str">
+      <c r="AB2" s="40"/>
+      <c r="AC2" s="39" t="str">
         <f>Calificacion!$B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AD2" s="37"/>
+      <c r="AD2" s="40"/>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="B3" s="41"/>
+      <c r="B3" s="36"/>
       <c r="C3" s="8" t="s">
         <v>1</v>
       </c>
@@ -2534,7 +2527,7 @@
     </row>
     <row r="4" spans="1:30" ht="76.900000000000006" x14ac:dyDescent="0.45">
       <c r="B4" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" s="27">
         <v>0</v>
@@ -2595,7 +2588,7 @@
     </row>
     <row r="5" spans="1:30" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B5" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C5" s="27"/>
       <c r="D5" s="28"/>
@@ -2628,7 +2621,7 @@
     </row>
     <row r="6" spans="1:30" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B6" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C6" s="27"/>
       <c r="D6" s="28"/>
@@ -2661,7 +2654,7 @@
     </row>
     <row r="7" spans="1:30" ht="46.15" x14ac:dyDescent="0.45">
       <c r="B7" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" s="27"/>
       <c r="D7" s="28"/>
@@ -2694,7 +2687,7 @@
     </row>
     <row r="8" spans="1:30" ht="92.25" x14ac:dyDescent="0.45">
       <c r="B8" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" s="27"/>
       <c r="D8" s="28"/>
@@ -2727,7 +2720,7 @@
     </row>
     <row r="9" spans="1:30" ht="61.5" x14ac:dyDescent="0.45">
       <c r="B9" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" s="31"/>
       <c r="D9" s="32"/>
@@ -2794,76 +2787,76 @@
       <c r="B11" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="38">
+      <c r="C11" s="37">
         <f>AVERAGE(C4:C10)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="39"/>
-      <c r="E11" s="38">
+      <c r="D11" s="38"/>
+      <c r="E11" s="37">
         <f>AVERAGE(E4:E10)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="39"/>
-      <c r="G11" s="38">
+      <c r="F11" s="38"/>
+      <c r="G11" s="37">
         <f>AVERAGE(G4:G10)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="39"/>
-      <c r="I11" s="38">
+      <c r="H11" s="38"/>
+      <c r="I11" s="37">
         <f>AVERAGE(I4:I10)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="39"/>
-      <c r="K11" s="38">
+      <c r="J11" s="38"/>
+      <c r="K11" s="37">
         <f>AVERAGE(K4:K10)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="39"/>
-      <c r="M11" s="38">
+      <c r="L11" s="38"/>
+      <c r="M11" s="37">
         <f>AVERAGE(M4:M10)</f>
         <v>0</v>
       </c>
-      <c r="N11" s="39"/>
-      <c r="O11" s="38">
+      <c r="N11" s="38"/>
+      <c r="O11" s="37">
         <f>AVERAGE(O4:O10)</f>
         <v>0</v>
       </c>
-      <c r="P11" s="39"/>
-      <c r="Q11" s="38">
+      <c r="P11" s="38"/>
+      <c r="Q11" s="37">
         <f>AVERAGE(Q4:Q10)</f>
         <v>0</v>
       </c>
-      <c r="R11" s="39"/>
-      <c r="S11" s="38">
+      <c r="R11" s="38"/>
+      <c r="S11" s="37">
         <f>AVERAGE(S4:S10)</f>
         <v>0</v>
       </c>
-      <c r="T11" s="39"/>
-      <c r="U11" s="38">
+      <c r="T11" s="38"/>
+      <c r="U11" s="37">
         <f>AVERAGE(U4:U10)</f>
         <v>0</v>
       </c>
-      <c r="V11" s="39"/>
-      <c r="W11" s="38">
+      <c r="V11" s="38"/>
+      <c r="W11" s="37">
         <f>AVERAGE(W4:W10)</f>
         <v>0</v>
       </c>
-      <c r="X11" s="39"/>
-      <c r="Y11" s="38">
+      <c r="X11" s="38"/>
+      <c r="Y11" s="37">
         <f>AVERAGE(Y4:Y10)</f>
         <v>0</v>
       </c>
-      <c r="Z11" s="39"/>
-      <c r="AA11" s="38">
+      <c r="Z11" s="38"/>
+      <c r="AA11" s="37">
         <f>AVERAGE(AA4:AA10)</f>
         <v>0</v>
       </c>
-      <c r="AB11" s="39"/>
-      <c r="AC11" s="38">
+      <c r="AB11" s="38"/>
+      <c r="AC11" s="37">
         <f>AVERAGE(AC4:AC10)</f>
         <v>0</v>
       </c>
-      <c r="AD11" s="39"/>
+      <c r="AD11" s="38"/>
     </row>
     <row r="12" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B12" s="16"/>
@@ -3983,19 +3976,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="AA11:AB11"/>
-    <mergeCell ref="Q11:R11"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="U11:V11"/>
-    <mergeCell ref="W11:X11"/>
-    <mergeCell ref="Y11:Z11"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="M11:N11"/>
     <mergeCell ref="AC2:AD2"/>
     <mergeCell ref="AC11:AD11"/>
     <mergeCell ref="C2:D2"/>
@@ -4012,6 +3992,19 @@
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="AA11:AB11"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="U11:V11"/>
+    <mergeCell ref="W11:X11"/>
+    <mergeCell ref="Y11:Z11"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="M11:N11"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/activity/M01A04/M01A04_MDT.xlsx
+++ b/activity/M01A04/M01A04_MDT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36DECA66-AF6E-4100-AAE7-ABECE0E10A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{802C53E2-CB00-4692-81A7-89AF34074AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
@@ -466,7 +466,7 @@
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -538,12 +538,6 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -574,11 +568,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="5" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -586,14 +583,11 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -699,11 +693,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Calificacion!$D$4</c:f>
+              <c:f>Calificacion!$F$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Calificación instructor</c:v>
+                  <c:v>Calificación final</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -715,16 +709,32 @@
               </a:schemeClr>
             </a:solidFill>
             <a:ln>
-              <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="95000"/>
-                  <a:alpha val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000000-D09F-4A1F-AD06-915152361BF4}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:dLbls>
             <c:spPr>
               <a:noFill/>
@@ -734,13 +744,13 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
@@ -752,7 +762,6 @@
                 <a:endParaRPr lang="es-CO"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="inBase"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
@@ -762,7 +771,21 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
               </c:ext>
             </c:extLst>
           </c:dLbls>
@@ -791,7 +814,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Calificacion!$D$5:$D$9</c:f>
+              <c:f>Calificacion!$F$5:$F$9</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="5"/>
@@ -2004,25 +2027,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="27" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
     </row>
     <row r="4" spans="2:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="17" t="s">
@@ -2052,7 +2075,7 @@
         <f>Detalle!C11*C5/5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="24"/>
+      <c r="E5" s="22"/>
       <c r="F5" s="13">
         <f>AVERAGE(D5:E5)</f>
         <v>0</v>
@@ -2069,7 +2092,7 @@
         <f>Detalle!E11*C6/5</f>
         <v>0</v>
       </c>
-      <c r="E6" s="24"/>
+      <c r="E6" s="22"/>
       <c r="F6" s="13">
         <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
         <v>0</v>
@@ -2086,7 +2109,7 @@
         <f>Detalle!G11*C7/5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="24"/>
+      <c r="E7" s="22"/>
       <c r="F7" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2103,7 +2126,7 @@
         <f>Detalle!I11*C8/5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="24"/>
+      <c r="E8" s="22"/>
       <c r="F8" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2120,7 +2143,7 @@
         <f>Detalle!K11*C9/5</f>
         <v>0</v>
       </c>
-      <c r="E9" s="24"/>
+      <c r="E9" s="22"/>
       <c r="F9" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2137,7 +2160,7 @@
         <f>Detalle!M11*C10/5</f>
         <v>0</v>
       </c>
-      <c r="E10" s="24"/>
+      <c r="E10" s="22"/>
       <c r="F10" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2154,7 +2177,7 @@
         <f>Detalle!O11*C11/5</f>
         <v>0</v>
       </c>
-      <c r="E11" s="24"/>
+      <c r="E11" s="22"/>
       <c r="F11" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2171,7 +2194,7 @@
         <f>Detalle!Q11*C12/5</f>
         <v>0</v>
       </c>
-      <c r="E12" s="24"/>
+      <c r="E12" s="22"/>
       <c r="F12" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2188,7 +2211,7 @@
         <f>Detalle!S11*C13/5</f>
         <v>0</v>
       </c>
-      <c r="E13" s="24"/>
+      <c r="E13" s="22"/>
       <c r="F13" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2205,7 +2228,7 @@
         <f>Detalle!U11*C14/5</f>
         <v>0</v>
       </c>
-      <c r="E14" s="24"/>
+      <c r="E14" s="22"/>
       <c r="F14" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2222,7 +2245,7 @@
         <f>Detalle!W11*C15/5</f>
         <v>0</v>
       </c>
-      <c r="E15" s="24"/>
+      <c r="E15" s="22"/>
       <c r="F15" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2239,7 +2262,7 @@
         <f>Detalle!Y11*C16/5</f>
         <v>0</v>
       </c>
-      <c r="E16" s="24"/>
+      <c r="E16" s="22"/>
       <c r="F16" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2256,7 +2279,7 @@
         <f>Detalle!AA11*C17/5</f>
         <v>0</v>
       </c>
-      <c r="E17" s="24"/>
+      <c r="E17" s="22"/>
       <c r="F17" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2273,35 +2296,35 @@
         <f>Detalle!AC11*C18/5</f>
         <v>0</v>
       </c>
-      <c r="E18" s="25"/>
+      <c r="E18" s="23"/>
       <c r="F18" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="41" t="str">
+      <c r="B19" s="33" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
         <v>Ir a actividad M01A04 en GitHub.</v>
       </c>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="41"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2364,82 +2387,82 @@
     </row>
     <row r="2" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="39" t="str">
+      <c r="C2" s="34" t="str">
         <f>Calificacion!$B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="40"/>
-      <c r="E2" s="39" t="str">
+      <c r="D2" s="35"/>
+      <c r="E2" s="34" t="str">
         <f>Calificacion!$B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="F2" s="40"/>
-      <c r="G2" s="39" t="str">
+      <c r="F2" s="35"/>
+      <c r="G2" s="34" t="str">
         <f>Calificacion!$B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="H2" s="40"/>
-      <c r="I2" s="39" t="str">
+      <c r="H2" s="35"/>
+      <c r="I2" s="34" t="str">
         <f>Calificacion!$B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="J2" s="40"/>
-      <c r="K2" s="39" t="str">
+      <c r="J2" s="35"/>
+      <c r="K2" s="34" t="str">
         <f>Calificacion!$B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="L2" s="40"/>
-      <c r="M2" s="39" t="str">
+      <c r="L2" s="35"/>
+      <c r="M2" s="34" t="str">
         <f>Calificacion!$B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="N2" s="40"/>
-      <c r="O2" s="39" t="str">
+      <c r="N2" s="35"/>
+      <c r="O2" s="34" t="str">
         <f>Calificacion!$B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="39" t="str">
+      <c r="P2" s="35"/>
+      <c r="Q2" s="34" t="str">
         <f>Calificacion!$B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="R2" s="40"/>
-      <c r="S2" s="39" t="str">
+      <c r="R2" s="35"/>
+      <c r="S2" s="34" t="str">
         <f>Calificacion!$B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="T2" s="40"/>
-      <c r="U2" s="39" t="str">
+      <c r="T2" s="35"/>
+      <c r="U2" s="34" t="str">
         <f>Calificacion!$B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="V2" s="40"/>
-      <c r="W2" s="39" t="str">
+      <c r="V2" s="35"/>
+      <c r="W2" s="34" t="str">
         <f>Calificacion!$B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="X2" s="40"/>
-      <c r="Y2" s="39" t="str">
+      <c r="X2" s="35"/>
+      <c r="Y2" s="34" t="str">
         <f>Calificacion!$B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="Z2" s="40"/>
-      <c r="AA2" s="39" t="str">
+      <c r="Z2" s="35"/>
+      <c r="AA2" s="34" t="str">
         <f>Calificacion!$B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AB2" s="40"/>
-      <c r="AC2" s="39" t="str">
+      <c r="AB2" s="35"/>
+      <c r="AC2" s="34" t="str">
         <f>Calificacion!$B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AD2" s="40"/>
+      <c r="AD2" s="35"/>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="B3" s="36"/>
+      <c r="B3" s="39"/>
       <c r="C3" s="8" t="s">
         <v>1</v>
       </c>
@@ -2529,334 +2552,334 @@
       <c r="B4" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="27">
-        <v>0</v>
-      </c>
-      <c r="D4" s="28"/>
-      <c r="E4" s="27">
-        <v>0</v>
-      </c>
-      <c r="F4" s="28"/>
-      <c r="G4" s="27">
-        <v>0</v>
-      </c>
-      <c r="H4" s="28"/>
-      <c r="I4" s="27">
-        <v>0</v>
-      </c>
-      <c r="J4" s="28"/>
-      <c r="K4" s="27">
-        <v>0</v>
-      </c>
-      <c r="L4" s="28"/>
-      <c r="M4" s="27">
-        <v>0</v>
-      </c>
-      <c r="N4" s="28"/>
-      <c r="O4" s="27">
-        <v>0</v>
-      </c>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="27">
-        <v>0</v>
-      </c>
-      <c r="R4" s="28"/>
-      <c r="S4" s="27">
-        <v>0</v>
-      </c>
-      <c r="T4" s="28"/>
-      <c r="U4" s="27">
-        <v>0</v>
-      </c>
-      <c r="V4" s="28"/>
-      <c r="W4" s="27">
-        <v>0</v>
-      </c>
-      <c r="X4" s="28"/>
-      <c r="Y4" s="27">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="28"/>
-      <c r="AA4" s="27">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="28"/>
-      <c r="AC4" s="27">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="28"/>
+      <c r="C4" s="25">
+        <v>0</v>
+      </c>
+      <c r="D4" s="26"/>
+      <c r="E4" s="25">
+        <v>0</v>
+      </c>
+      <c r="F4" s="26"/>
+      <c r="G4" s="25">
+        <v>0</v>
+      </c>
+      <c r="H4" s="26"/>
+      <c r="I4" s="25">
+        <v>0</v>
+      </c>
+      <c r="J4" s="26"/>
+      <c r="K4" s="25">
+        <v>0</v>
+      </c>
+      <c r="L4" s="26"/>
+      <c r="M4" s="25">
+        <v>0</v>
+      </c>
+      <c r="N4" s="26"/>
+      <c r="O4" s="25">
+        <v>0</v>
+      </c>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="25">
+        <v>0</v>
+      </c>
+      <c r="R4" s="26"/>
+      <c r="S4" s="25">
+        <v>0</v>
+      </c>
+      <c r="T4" s="26"/>
+      <c r="U4" s="25">
+        <v>0</v>
+      </c>
+      <c r="V4" s="26"/>
+      <c r="W4" s="25">
+        <v>0</v>
+      </c>
+      <c r="X4" s="26"/>
+      <c r="Y4" s="25">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="26"/>
+      <c r="AA4" s="25">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="26"/>
+      <c r="AC4" s="25">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="26"/>
     </row>
     <row r="5" spans="1:30" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="27"/>
-      <c r="N5" s="28"/>
-      <c r="O5" s="27"/>
-      <c r="P5" s="28"/>
-      <c r="Q5" s="27"/>
-      <c r="R5" s="28"/>
-      <c r="S5" s="27"/>
-      <c r="T5" s="28"/>
-      <c r="U5" s="27"/>
-      <c r="V5" s="28"/>
-      <c r="W5" s="27"/>
-      <c r="X5" s="28"/>
-      <c r="Y5" s="27"/>
-      <c r="Z5" s="28"/>
-      <c r="AA5" s="27"/>
-      <c r="AB5" s="28"/>
-      <c r="AC5" s="27"/>
-      <c r="AD5" s="28"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="26"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="26"/>
+      <c r="Q5" s="25"/>
+      <c r="R5" s="26"/>
+      <c r="S5" s="25"/>
+      <c r="T5" s="26"/>
+      <c r="U5" s="25"/>
+      <c r="V5" s="26"/>
+      <c r="W5" s="25"/>
+      <c r="X5" s="26"/>
+      <c r="Y5" s="25"/>
+      <c r="Z5" s="26"/>
+      <c r="AA5" s="25"/>
+      <c r="AB5" s="26"/>
+      <c r="AC5" s="25"/>
+      <c r="AD5" s="26"/>
     </row>
     <row r="6" spans="1:30" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B6" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="27"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="27"/>
-      <c r="N6" s="28"/>
-      <c r="O6" s="27"/>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="27"/>
-      <c r="R6" s="28"/>
-      <c r="S6" s="27"/>
-      <c r="T6" s="28"/>
-      <c r="U6" s="27"/>
-      <c r="V6" s="28"/>
-      <c r="W6" s="27"/>
-      <c r="X6" s="28"/>
-      <c r="Y6" s="27"/>
-      <c r="Z6" s="28"/>
-      <c r="AA6" s="27"/>
-      <c r="AB6" s="28"/>
-      <c r="AC6" s="27"/>
-      <c r="AD6" s="28"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="26"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="26"/>
+      <c r="O6" s="25"/>
+      <c r="P6" s="26"/>
+      <c r="Q6" s="25"/>
+      <c r="R6" s="26"/>
+      <c r="S6" s="25"/>
+      <c r="T6" s="26"/>
+      <c r="U6" s="25"/>
+      <c r="V6" s="26"/>
+      <c r="W6" s="25"/>
+      <c r="X6" s="26"/>
+      <c r="Y6" s="25"/>
+      <c r="Z6" s="26"/>
+      <c r="AA6" s="25"/>
+      <c r="AB6" s="26"/>
+      <c r="AC6" s="25"/>
+      <c r="AD6" s="26"/>
     </row>
     <row r="7" spans="1:30" ht="46.15" x14ac:dyDescent="0.45">
       <c r="B7" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="27"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="27"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="27"/>
-      <c r="N7" s="28"/>
-      <c r="O7" s="27"/>
-      <c r="P7" s="28"/>
-      <c r="Q7" s="27"/>
-      <c r="R7" s="28"/>
-      <c r="S7" s="27"/>
-      <c r="T7" s="28"/>
-      <c r="U7" s="27"/>
-      <c r="V7" s="28"/>
-      <c r="W7" s="27"/>
-      <c r="X7" s="28"/>
-      <c r="Y7" s="27"/>
-      <c r="Z7" s="28"/>
-      <c r="AA7" s="27"/>
-      <c r="AB7" s="28"/>
-      <c r="AC7" s="27"/>
-      <c r="AD7" s="28"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="26"/>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="26"/>
+      <c r="S7" s="25"/>
+      <c r="T7" s="26"/>
+      <c r="U7" s="25"/>
+      <c r="V7" s="26"/>
+      <c r="W7" s="25"/>
+      <c r="X7" s="26"/>
+      <c r="Y7" s="25"/>
+      <c r="Z7" s="26"/>
+      <c r="AA7" s="25"/>
+      <c r="AB7" s="26"/>
+      <c r="AC7" s="25"/>
+      <c r="AD7" s="26"/>
     </row>
     <row r="8" spans="1:30" ht="92.25" x14ac:dyDescent="0.45">
       <c r="B8" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="27"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="27"/>
-      <c r="L8" s="28"/>
-      <c r="M8" s="27"/>
-      <c r="N8" s="28"/>
-      <c r="O8" s="27"/>
-      <c r="P8" s="28"/>
-      <c r="Q8" s="27"/>
-      <c r="R8" s="28"/>
-      <c r="S8" s="27"/>
-      <c r="T8" s="28"/>
-      <c r="U8" s="27"/>
-      <c r="V8" s="28"/>
-      <c r="W8" s="27"/>
-      <c r="X8" s="28"/>
-      <c r="Y8" s="27"/>
-      <c r="Z8" s="28"/>
-      <c r="AA8" s="27"/>
-      <c r="AB8" s="28"/>
-      <c r="AC8" s="27"/>
-      <c r="AD8" s="28"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="25"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="26"/>
+      <c r="S8" s="25"/>
+      <c r="T8" s="26"/>
+      <c r="U8" s="25"/>
+      <c r="V8" s="26"/>
+      <c r="W8" s="25"/>
+      <c r="X8" s="26"/>
+      <c r="Y8" s="25"/>
+      <c r="Z8" s="26"/>
+      <c r="AA8" s="25"/>
+      <c r="AB8" s="26"/>
+      <c r="AC8" s="25"/>
+      <c r="AD8" s="26"/>
     </row>
     <row r="9" spans="1:30" ht="61.5" x14ac:dyDescent="0.45">
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="31"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="32"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="32"/>
-      <c r="M9" s="31"/>
-      <c r="N9" s="32"/>
-      <c r="O9" s="31"/>
-      <c r="P9" s="32"/>
-      <c r="Q9" s="31"/>
-      <c r="R9" s="32"/>
-      <c r="S9" s="31"/>
-      <c r="T9" s="32"/>
-      <c r="U9" s="31"/>
-      <c r="V9" s="32"/>
-      <c r="W9" s="31"/>
-      <c r="X9" s="32"/>
-      <c r="Y9" s="31"/>
-      <c r="Z9" s="32"/>
-      <c r="AA9" s="31"/>
-      <c r="AB9" s="32"/>
-      <c r="AC9" s="31"/>
-      <c r="AD9" s="32"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="29"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="30"/>
+      <c r="Q9" s="29"/>
+      <c r="R9" s="30"/>
+      <c r="S9" s="29"/>
+      <c r="T9" s="30"/>
+      <c r="U9" s="29"/>
+      <c r="V9" s="30"/>
+      <c r="W9" s="29"/>
+      <c r="X9" s="30"/>
+      <c r="Y9" s="29"/>
+      <c r="Z9" s="30"/>
+      <c r="AA9" s="29"/>
+      <c r="AB9" s="30"/>
+      <c r="AC9" s="29"/>
+      <c r="AD9" s="30"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="B10" s="30"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="32"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="32"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="32"/>
-      <c r="O10" s="31"/>
-      <c r="P10" s="32"/>
-      <c r="Q10" s="31"/>
-      <c r="R10" s="32"/>
-      <c r="S10" s="31"/>
-      <c r="T10" s="32"/>
-      <c r="U10" s="31"/>
-      <c r="V10" s="32"/>
-      <c r="W10" s="31"/>
-      <c r="X10" s="32"/>
-      <c r="Y10" s="31"/>
-      <c r="Z10" s="32"/>
-      <c r="AA10" s="31"/>
-      <c r="AB10" s="32"/>
-      <c r="AC10" s="31"/>
-      <c r="AD10" s="32"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="29"/>
+      <c r="P10" s="30"/>
+      <c r="Q10" s="29"/>
+      <c r="R10" s="30"/>
+      <c r="S10" s="29"/>
+      <c r="T10" s="30"/>
+      <c r="U10" s="29"/>
+      <c r="V10" s="30"/>
+      <c r="W10" s="29"/>
+      <c r="X10" s="30"/>
+      <c r="Y10" s="29"/>
+      <c r="Z10" s="30"/>
+      <c r="AA10" s="29"/>
+      <c r="AB10" s="30"/>
+      <c r="AC10" s="29"/>
+      <c r="AD10" s="30"/>
     </row>
     <row r="11" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A11" s="1"/>
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="37">
+      <c r="C11" s="36">
         <f>AVERAGE(C4:C10)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="38"/>
-      <c r="E11" s="37">
+      <c r="D11" s="37"/>
+      <c r="E11" s="36">
         <f>AVERAGE(E4:E10)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="38"/>
-      <c r="G11" s="37">
+      <c r="F11" s="37"/>
+      <c r="G11" s="36">
         <f>AVERAGE(G4:G10)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="38"/>
-      <c r="I11" s="37">
+      <c r="H11" s="37"/>
+      <c r="I11" s="36">
         <f>AVERAGE(I4:I10)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="38"/>
-      <c r="K11" s="37">
+      <c r="J11" s="37"/>
+      <c r="K11" s="36">
         <f>AVERAGE(K4:K10)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="38"/>
-      <c r="M11" s="37">
+      <c r="L11" s="37"/>
+      <c r="M11" s="36">
         <f>AVERAGE(M4:M10)</f>
         <v>0</v>
       </c>
-      <c r="N11" s="38"/>
-      <c r="O11" s="37">
+      <c r="N11" s="37"/>
+      <c r="O11" s="36">
         <f>AVERAGE(O4:O10)</f>
         <v>0</v>
       </c>
-      <c r="P11" s="38"/>
-      <c r="Q11" s="37">
+      <c r="P11" s="37"/>
+      <c r="Q11" s="36">
         <f>AVERAGE(Q4:Q10)</f>
         <v>0</v>
       </c>
-      <c r="R11" s="38"/>
-      <c r="S11" s="37">
+      <c r="R11" s="37"/>
+      <c r="S11" s="36">
         <f>AVERAGE(S4:S10)</f>
         <v>0</v>
       </c>
-      <c r="T11" s="38"/>
-      <c r="U11" s="37">
+      <c r="T11" s="37"/>
+      <c r="U11" s="36">
         <f>AVERAGE(U4:U10)</f>
         <v>0</v>
       </c>
-      <c r="V11" s="38"/>
-      <c r="W11" s="37">
+      <c r="V11" s="37"/>
+      <c r="W11" s="36">
         <f>AVERAGE(W4:W10)</f>
         <v>0</v>
       </c>
-      <c r="X11" s="38"/>
-      <c r="Y11" s="37">
+      <c r="X11" s="37"/>
+      <c r="Y11" s="36">
         <f>AVERAGE(Y4:Y10)</f>
         <v>0</v>
       </c>
-      <c r="Z11" s="38"/>
-      <c r="AA11" s="37">
+      <c r="Z11" s="37"/>
+      <c r="AA11" s="36">
         <f>AVERAGE(AA4:AA10)</f>
         <v>0</v>
       </c>
-      <c r="AB11" s="38"/>
-      <c r="AC11" s="37">
+      <c r="AB11" s="37"/>
+      <c r="AC11" s="36">
         <f>AVERAGE(AC4:AC10)</f>
         <v>0</v>
       </c>
-      <c r="AD11" s="38"/>
+      <c r="AD11" s="37"/>
     </row>
     <row r="12" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B12" s="16"/>
@@ -3976,6 +3999,19 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="AA11:AB11"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="U11:V11"/>
+    <mergeCell ref="W11:X11"/>
+    <mergeCell ref="Y11:Z11"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="M11:N11"/>
     <mergeCell ref="AC2:AD2"/>
     <mergeCell ref="AC11:AD11"/>
     <mergeCell ref="C2:D2"/>
@@ -3992,19 +4028,6 @@
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="I2:J2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="AA11:AB11"/>
-    <mergeCell ref="Q11:R11"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="U11:V11"/>
-    <mergeCell ref="W11:X11"/>
-    <mergeCell ref="Y11:Z11"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="M11:N11"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
